--- a/output/pdf_financials_xlsx/GFR.xlsx
+++ b/output/pdf_financials_xlsx/GFR.xlsx
@@ -9169,11 +9169,11 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>-0.439604</v>
+        <v>0.439604</v>
       </c>
       <c r="F140" s="5" t="n">
         <v>0.78329</v>

--- a/output/pdf_financials_xlsx/GFR.xlsx
+++ b/output/pdf_financials_xlsx/GFR.xlsx
@@ -782,10 +782,10 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.087681</v>
+        <v>-0.087681</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.019386</v>
+        <v>0.019386</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0.084879</v>
@@ -1912,13 +1912,13 @@
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.05985</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>61.804</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>88.432</v>
       </c>
     </row>
     <row r="65">
@@ -1981,16 +1981,16 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.030401</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.040429</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>45.176</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>77.19199999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2971,16 +2971,16 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.000298</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.000743</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.06360399999999999</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.014554</v>
       </c>
       <c r="F110" s="3" t="n">
         <v>0</v>
@@ -6883,7 +6883,11 @@
           <t>Accretion 14</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -7416,7 +7420,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E95" s="5" t="n">
         <v>0.661444</v>
       </c>
@@ -7695,7 +7703,11 @@
           <t>Accretion 13</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E102" s="5" t="n">
         <v>0.000298</v>
       </c>
@@ -10308,7 +10320,11 @@
           <t>Income tax recovery (expense) 6</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -11344,7 +11360,11 @@
           <t>Income tax recovery (expense) 12</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
